--- a/docs/samples/import_report.xlsx
+++ b/docs/samples/import_report.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-23 06:28</t>
+          <t>2026-09-23 08:30</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -625,7 +625,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-23 06:28</t>
+          <t>2026-09-23 08:30</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -688,7 +688,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-23 06:28</t>
+          <t>2026-09-23 08:30</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -751,7 +751,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-23 06:28</t>
+          <t>2026-09-23 08:30</t>
         </is>
       </c>
       <c r="F5" t="n">

--- a/docs/samples/import_report.xlsx
+++ b/docs/samples/import_report.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-23 08:30</t>
+          <t>2026-09-23 14:12</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -595,7 +595,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026.09-1</t>
+          <t>2026.09-2</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-23 08:30</t>
+          <t>2026-09-23 14:12</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -658,7 +658,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026.09-1</t>
+          <t>2026.09-2</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-23 08:30</t>
+          <t>2026-09-23 14:12</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -721,7 +721,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026.09-1</t>
+          <t>2026.09-2</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-23 08:30</t>
+          <t>2026-09-23 14:12</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -784,7 +784,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026.09-1</t>
+          <t>2026.09-2</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1990,7 +1990,7 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MISSING_CURRENCY, MISSING_OE, MISSING_PRICE</t>
+          <t>MISSING_CURRENCY, MISSING_OE, MISSING_PRICE, SUSPECTED_NAME_ERROR</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,11 @@
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>SUSPECTED_NAME_ERROR</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">

--- a/docs/samples/import_report.xlsx
+++ b/docs/samples/import_report.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-23 14:12</t>
+          <t>2026-09-23 23:50</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -625,7 +625,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-23 14:12</t>
+          <t>2026-09-23 23:50</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -688,7 +688,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-23 14:12</t>
+          <t>2026-09-23 23:50</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -698,13 +698,13 @@
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -726,7 +726,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>4601cb5d75e62532</t>
+          <t>05bb36358d92c7fc</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-23 14:12</t>
+          <t>2026-09-23 23:50</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -2220,17 +2220,13 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>冲突</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>关键属性变化：dims: [151.0, 91.0, 14.0] → [151.0, 91.0, 20.0]</t>
-        </is>
-      </c>
+          <t>更新</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>KEY_ATTR_CHANGED</t>
+          <t>PACKAGE_DIMS_CHANGED</t>
         </is>
       </c>
     </row>
@@ -2360,11 +2356,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>未变</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+          <t>冲突</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>关键属性变化：fitment: Volvo VN 2004-2017 → Volvo VN 2006-2017</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>KEY_ATTR_CHANGED</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">

--- a/docs/samples/import_report.xlsx
+++ b/docs/samples/import_report.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-23 23:50</t>
+          <t>2026-09-24 00:41</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -625,7 +625,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-23 23:50</t>
+          <t>2026-09-24 00:41</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -688,7 +688,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-23 23:50</t>
+          <t>2026-09-24 00:41</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -751,7 +751,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-23 23:50</t>
+          <t>2026-09-24 00:41</t>
         </is>
       </c>
       <c r="F5" t="n">

--- a/docs/samples/import_report.xlsx
+++ b/docs/samples/import_report.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-24 00:41</t>
+          <t>2026-09-28 16:40</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -625,7 +625,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-24 00:41</t>
+          <t>2026-09-28 16:40</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -688,7 +688,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-24 00:41</t>
+          <t>2026-09-28 16:40</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -751,7 +751,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-24 00:41</t>
+          <t>2026-09-28 16:40</t>
         </is>
       </c>
       <c r="F5" t="n">
